--- a/ig/main/ValueSet-jdv-j394-type-demande-compensation-ms.xlsx
+++ b/ig/main/ValueSet-jdv-j394-type-demande-compensation-ms.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -66,15 +67,12 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00.000+00:00</t>
+    <t>2026-05-29T09:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -84,9 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Type demande de compensation adressée à la CDAPH.</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -99,25 +94,160 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r417-type-demande-compensation|20260505120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>warning-draft</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j394-type-demande-compensation-ms|20260505120000</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r417-type-demande-compensation</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>ACFP (Allocation Compensatrice pour frais professionnels)</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>ACTP (Allocation Compensatrice pour Tierce Personne)</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>Allocation aux adultes handicapés et complément de ressources - AAH</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>Allocation aux adultes handicapés et complément de ressources - Complément de ressources</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Allocation d'éducation de l'enfant handicapé (AEEH) et son complément</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>AVA (Affiliation gratuite à l'assurance vieillesse des aidants)</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion - Invalidité ou priorité</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion - Stationnement</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Maintien en ESMS au titre de l'amendement Creton</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Emploi accompagné</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Etablissement et service d'accompagnement par le travail (ESAT)</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Etablissement ou service de réadaptation professionnelle (ESRP), Etablissement ou service de préorientation (ESPO) ou Unité d’évaluation, de réentraînement et d’orientation sociale et socioprofessionnelle pour personnes cérébro-lésées (UEROS)</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Marché du travail</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Orientation vers un établissement ou service médico-social (ESMS) pour adultes</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Parcours de scolarisation et/ou de formation avec ou sans accompagnement par un établissement ou service médico-social</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>PCH aide humaine à la parentalité simplifiée</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>PCH aides techniques à la parentalité simplifiée</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>PCH parentalité simplifiée</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>RQTH (Reconnaissance de la qualité de travailleur handicapé)</t>
   </si>
 </sst>
 </file>
@@ -334,44 +464,40 @@
       <c r="A10" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -381,49 +507,479 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>33</v>
       </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-j394-type-demande-compensation-ms.xlsx
+++ b/ig/main/ValueSet-jdv-j394-type-demande-compensation-ms.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="85">
   <si>
     <t>Property</t>
   </si>
@@ -118,6 +120,156 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r417-type-demande-compensation</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r417-type-demande-compensation|20260505120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>warning-draft</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>ACFP (Allocation Compensatrice pour frais professionnels)</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>ACTP (Allocation Compensatrice pour Tierce Personne)</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>Allocation aux adultes handicapés et complément de ressources - AAH</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>Allocation aux adultes handicapés et complément de ressources - Complément de ressources</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Allocation d'éducation de l'enfant handicapé (AEEH) et son complément</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>AVA (Affiliation gratuite à l'assurance vieillesse des aidants)</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion - Invalidité ou priorité</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Carte mobilité inclusion - Stationnement</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Maintien en ESMS au titre de l'amendement Creton</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Emploi accompagné</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Etablissement et service d'accompagnement par le travail (ESAT)</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Etablissement ou service de réadaptation professionnelle (ESRP), Etablissement ou service de préorientation (ESPO) ou Unité d’évaluation, de réentraînement et d’orientation sociale et socioprofessionnelle pour personnes cérébro-lésées (UEROS)</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>Orientation professionnelle - Marché du travail</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Orientation vers un établissement ou service médico-social (ESMS) pour adultes</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Parcours de scolarisation et/ou de formation avec ou sans accompagnement par un établissement ou service médico-social</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>PCH aide humaine à la parentalité simplifiée</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>PCH aides techniques à la parentalité simplifiée</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>PCH parentalité simplifiée</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>RQTH (Reconnaissance de la qualité de travailleur handicapé)</t>
   </si>
 </sst>
 </file>
@@ -429,4 +581,478 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>